--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACF3BC3-9B95-4A9B-B91B-8E2926E16FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58598246-668D-49D7-964A-2288E8681440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="222">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -702,6 +702,12 @@
   </si>
   <si>
     <t>Flare</t>
+  </si>
+  <si>
+    <t>Blast</t>
+  </si>
+  <si>
+    <t>Valkyrie</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1135,6 +1141,11 @@
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -1144,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FD2484-138B-46C2-8DC8-D65120EDD404}">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -1468,6 +1479,11 @@
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58598246-668D-49D7-964A-2288E8681440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E2B6D3-D183-4CEC-B4F4-851112CFB5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
@@ -1183,307 +1183,307 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>219</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E2B6D3-D183-4CEC-B4F4-851112CFB5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8482A5C2-9CF1-417D-B3E5-8FBAD4EB19EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="268">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -708,6 +708,144 @@
   </si>
   <si>
     <t>Valkyrie</t>
+  </si>
+  <si>
+    <t>Hover Wyvern</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Bumblebee</t>
+  </si>
+  <si>
+    <t>Captain America</t>
+  </si>
+  <si>
+    <t>Chewbacca</t>
+  </si>
+  <si>
+    <t>Darth Vader</t>
+  </si>
+  <si>
+    <t>Eclipse</t>
+  </si>
+  <si>
+    <t>General Grievous</t>
+  </si>
+  <si>
+    <t>Gill Shark</t>
+  </si>
+  <si>
+    <t>Green Goblin</t>
+  </si>
+  <si>
+    <t>Hunt</t>
+  </si>
+  <si>
+    <t>Iron Man</t>
+  </si>
+  <si>
+    <t>Luke Skywalker</t>
+  </si>
+  <si>
+    <t>Megatron</t>
+  </si>
+  <si>
+    <t>Meteor Dragoon</t>
+  </si>
+  <si>
+    <t>Miles Morales</t>
+  </si>
+  <si>
+    <t>Moff Gideon</t>
+  </si>
+  <si>
+    <t>Mosasaurus</t>
+  </si>
+  <si>
+    <t>Mummy Curse</t>
+  </si>
+  <si>
+    <t>Obi-Wan Kenobi</t>
+  </si>
+  <si>
+    <t>Optimus Primal</t>
+  </si>
+  <si>
+    <t>Optimus Prime</t>
+  </si>
+  <si>
+    <t>Perseus Dark</t>
+  </si>
+  <si>
+    <t>Red Hulk</t>
+  </si>
+  <si>
+    <t>Ring Aether</t>
+  </si>
+  <si>
+    <t>Savage Bear</t>
+  </si>
+  <si>
+    <t>Shockwave</t>
+  </si>
+  <si>
+    <t>Spider-Man</t>
+  </si>
+  <si>
+    <t>Spinosaurus</t>
+  </si>
+  <si>
+    <t>Starscream</t>
+  </si>
+  <si>
+    <t>Stone Mont Blanc</t>
+  </si>
+  <si>
+    <t>Stormtrooper</t>
+  </si>
+  <si>
+    <t>Strike Hawk</t>
+  </si>
+  <si>
+    <t>T. Rex</t>
+  </si>
+  <si>
+    <t>Tackle Goat</t>
+  </si>
+  <si>
+    <t>Thanos</t>
+  </si>
+  <si>
+    <t>The Mandalorian</t>
+  </si>
+  <si>
+    <t>Trypio</t>
+  </si>
+  <si>
+    <t>Venom</t>
+  </si>
+  <si>
+    <t>Very Berry Bomb</t>
+  </si>
+  <si>
+    <t>Stag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antler </t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>Kraken</t>
+  </si>
+  <si>
+    <t>Wriggle</t>
+  </si>
+  <si>
+    <t>Hack Viking</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1146,6 +1284,21 @@
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -1155,11 +1308,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FD2484-138B-46C2-8DC8-D65120EDD404}">
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1168,321 +1318,534 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>233</v>
+      </c>
+      <c r="G39" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>86</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>88</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>243</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>96</v>
+        <v>245</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>97</v>
       </c>
     </row>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -8,19 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8482A5C2-9CF1-417D-B3E5-8FBAD4EB19EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA640F-417C-489C-9534-E30AAD8C95B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
-    <sheet name="Blades (BX, UX, CX Main)" sheetId="3" r:id="rId2"/>
-    <sheet name="Over Blades" sheetId="2" r:id="rId3"/>
-    <sheet name="Metal Blades" sheetId="4" r:id="rId4"/>
-    <sheet name="Assist Blades" sheetId="5" r:id="rId5"/>
-    <sheet name="Ratchets" sheetId="6" r:id="rId6"/>
-    <sheet name="Bits" sheetId="7" r:id="rId7"/>
+    <sheet name="Blades BX-UX" sheetId="3" r:id="rId2"/>
+    <sheet name="Blades CX" sheetId="9" r:id="rId3"/>
+    <sheet name="Over Blades" sheetId="2" r:id="rId4"/>
+    <sheet name="Metal Blades" sheetId="4" r:id="rId5"/>
+    <sheet name="Assist Blades" sheetId="5" r:id="rId6"/>
+    <sheet name="Ratchets" sheetId="6" r:id="rId7"/>
+    <sheet name="Bits" sheetId="7" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blades BX-UX'!$A$1:$A$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blades CX'!$A$1:$A$15</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="274">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -846,6 +851,24 @@
   </si>
   <si>
     <t>Hack Viking</t>
+  </si>
+  <si>
+    <t>Flame</t>
+  </si>
+  <si>
+    <t>Cerebrus</t>
+  </si>
+  <si>
+    <t>Whale</t>
+  </si>
+  <si>
+    <t>Volt</t>
+  </si>
+  <si>
+    <t>Might</t>
+  </si>
+  <si>
+    <t>Fang</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1228,76 +1251,86 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>266</v>
       </c>
     </row>
@@ -1308,8 +1341,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FD2484-138B-46C2-8DC8-D65120EDD404}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1318,534 +1354,479 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>262</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>233</v>
-      </c>
-      <c r="G39" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>236</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>237</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>238</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>239</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>241</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>243</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>70</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>246</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>251</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>252</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>255</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>257</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>258</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>259</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1855,6 +1836,91 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B0DAFC-13DE-46FF-A141-B64698BB60AB}">
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A94B30-4A05-4913-869B-F7BDD7653D72}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1882,7 +1948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894BAF9-FB4B-452B-BF9F-6F9CCE9B55C8}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1915,7 +1981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408C55BD-65AC-48B0-AA3B-58B5A03C3D58}">
   <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2233,7 +2299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F160EA4-7BEC-4BAF-AD34-499815061A5E}">
   <dimension ref="A1:A63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2557,7 +2623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
   <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA640F-417C-489C-9534-E30AAD8C95B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2821EA58-9C19-4561-9ED2-8845F156DACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="273">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -413,9 +413,6 @@
   </si>
   <si>
     <t>Lightning L-Drago (Rapid)</t>
-  </si>
-  <si>
-    <t>Metal Blade</t>
   </si>
   <si>
     <t>High Ball</t>
@@ -1246,92 +1243,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -1364,17 +1361,17 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -1399,7 +1396,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -1439,7 +1436,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1449,7 +1446,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1459,12 +1456,12 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1484,7 +1481,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1494,7 +1491,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1502,7 +1499,7 @@
         <v>50</v>
       </c>
       <c r="G31" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1537,7 +1534,7 @@
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
@@ -1547,52 +1544,52 @@
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -1617,7 +1614,7 @@
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
@@ -1627,7 +1624,7 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
@@ -1637,7 +1634,7 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
@@ -1652,7 +1649,7 @@
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
@@ -1667,7 +1664,7 @@
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
@@ -1687,7 +1684,7 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
@@ -1702,22 +1699,22 @@
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
@@ -1727,32 +1724,32 @@
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
@@ -1762,7 +1759,7 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
@@ -1777,12 +1774,12 @@
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
@@ -1847,7 +1844,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -1867,37 +1864,37 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -1907,12 +1904,12 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894BAF9-FB4B-452B-BF9F-6F9CCE9B55C8}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -1958,21 +1955,16 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2036,12 +2028,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -2324,162 +2316,162 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -2633,10 +2625,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" t="s">
         <v>172</v>
-      </c>
-      <c r="B1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2644,7 +2636,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2652,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2660,7 +2652,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2668,7 +2660,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2676,7 +2668,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2684,7 +2676,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2692,7 +2684,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2700,7 +2692,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2708,7 +2700,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2716,7 +2708,7 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2724,7 +2716,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2732,7 +2724,7 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2740,7 +2732,7 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2748,7 +2740,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2756,7 +2748,7 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2764,15 +2756,15 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2780,7 +2772,7 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2788,7 +2780,7 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2796,15 +2788,15 @@
         <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2812,7 +2804,7 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2820,7 +2812,7 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2828,7 +2820,7 @@
         <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2836,7 +2828,7 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2844,7 +2836,7 @@
         <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2852,7 +2844,7 @@
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2860,7 +2852,7 @@
         <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2868,7 +2860,7 @@
         <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2876,7 +2868,7 @@
         <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2884,7 +2876,7 @@
         <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2892,7 +2884,7 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2900,15 +2892,15 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2916,7 +2908,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2924,7 +2916,7 @@
         <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2932,7 +2924,7 @@
         <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2940,7 +2932,7 @@
         <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2948,7 +2940,7 @@
         <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2956,7 +2948,7 @@
         <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2964,7 +2956,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2972,7 +2964,7 @@
         <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2980,7 +2972,7 @@
         <v>120</v>
       </c>
       <c r="B44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2988,7 +2980,7 @@
         <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2821EA58-9C19-4561-9ED2-8845F156DACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C8F97-AD05-4C3F-866C-8C38D5E40B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" activeTab="7" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="277">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -866,6 +866,18 @@
   </si>
   <si>
     <t>Fang</t>
+  </si>
+  <si>
+    <t>Under Flat</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Trans Kick</t>
+  </si>
+  <si>
+    <t>TK</t>
   </si>
 </sst>
 </file>
@@ -2617,7 +2629,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -2983,6 +2995,22 @@
         <v>216</v>
       </c>
     </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>273</v>
+      </c>
+      <c r="B46" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>275</v>
+      </c>
+      <c r="B47" t="s">
+        <v>276</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10403"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C8F97-AD05-4C3F-866C-8C38D5E40B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" activeTab="7" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blades BX-UX'!$A$1:$A$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blades CX'!$A$1:$A$15</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="278">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -878,6 +878,9 @@
   </si>
   <si>
     <t>TK</t>
+  </si>
+  <si>
+    <t>Sol</t>
   </si>
 </sst>
 </file>
@@ -1250,97 +1253,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -1351,162 +1359,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FD2484-138B-46C2-8DC8-D65120EDD404}">
   <dimension ref="A1:G96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.80859375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -1514,327 +1522,327 @@
         <v>222</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -1847,79 +1855,79 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B0DAFC-13DE-46FF-A141-B64698BB60AB}">
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>270</v>
       </c>
@@ -1932,22 +1940,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A94B30-4A05-4913-869B-F7BDD7653D72}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.35546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -1960,22 +1968,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894BAF9-FB4B-452B-BF9F-6F9CCE9B55C8}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>105</v>
       </c>
@@ -1988,312 +1996,312 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408C55BD-65AC-48B0-AA3B-58B5A03C3D58}">
   <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>107</v>
       </c>
@@ -2306,320 +2314,320 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F160EA4-7BEC-4BAF-AD34-499815061A5E}">
   <dimension ref="A1:A63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.609375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63"/>
     </row>
   </sheetData>
@@ -2630,12 +2638,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>171</v>
       </c>
@@ -2643,7 +2651,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2651,7 +2659,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2659,7 +2667,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -2667,7 +2675,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2675,7 +2683,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2683,7 +2691,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2691,7 +2699,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2699,7 +2707,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2707,7 +2715,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -2715,7 +2723,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -2723,7 +2731,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2731,7 +2739,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2739,7 +2747,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2747,7 +2755,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -2755,7 +2763,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2763,7 +2771,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2771,7 +2779,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>122</v>
       </c>
@@ -2779,7 +2787,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2787,7 +2795,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -2795,7 +2803,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -2803,7 +2811,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>123</v>
       </c>
@@ -2811,7 +2819,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2819,7 +2827,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2827,7 +2835,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -2835,7 +2843,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -2843,7 +2851,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -2851,7 +2859,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -2859,7 +2867,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -2867,7 +2875,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -2875,7 +2883,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -2883,7 +2891,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -2891,7 +2899,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -2899,7 +2907,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -2907,7 +2915,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>124</v>
       </c>
@@ -2915,7 +2923,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -2923,7 +2931,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -2931,7 +2939,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -2939,7 +2947,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -2947,7 +2955,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -2955,7 +2963,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -2963,7 +2971,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -2971,7 +2979,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2979,7 +2987,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>120</v>
       </c>
@@ -2987,7 +2995,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2995,7 +3003,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>273</v>
       </c>
@@ -3003,7 +3011,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>275</v>
       </c>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C8F97-AD05-4C3F-866C-8C38D5E40B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" activeTab="5" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="280">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -881,6 +881,12 @@
   </si>
   <si>
     <t>Sol</t>
+  </si>
+  <si>
+    <t>Zillion</t>
+  </si>
+  <si>
+    <t>Assault</t>
   </si>
 </sst>
 </file>
@@ -2058,12 +2064,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\Backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8D3942-0E12-4843-8081-ACA18F82DEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C359D0E2-88CC-4542-BBAC-8A734D98C16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="2505" windowWidth="25500" windowHeight="18375" activeTab="7" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="2" activeTab="7" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Bits" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Bits!$A$1:$B$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blades BX-UX'!$A$1:$A$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blades CX'!$A$1:$A$15</definedName>
   </definedNames>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="272">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -79,9 +80,6 @@
     <t>Cyclone</t>
   </si>
   <si>
-    <t>Disc Ball</t>
-  </si>
-  <si>
     <t>Dot</t>
   </si>
   <si>
@@ -109,9 +107,6 @@
     <t>Gear Flat</t>
   </si>
   <si>
-    <t>Croco Crunch</t>
-  </si>
-  <si>
     <t>Gear Needle</t>
   </si>
   <si>
@@ -265,9 +260,6 @@
     <t>Wedge</t>
   </si>
   <si>
-    <t>Ptera Swing</t>
-  </si>
-  <si>
     <t>Zap</t>
   </si>
   <si>
@@ -415,15 +407,6 @@
     <t>Lightning L-Drago (Rapid)</t>
   </si>
   <si>
-    <t>High Ball</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Rubber Dash</t>
-  </si>
-  <si>
     <t>1-50</t>
   </si>
   <si>
@@ -502,9 +485,6 @@
     <t>7-80</t>
   </si>
   <si>
-    <t>8-60</t>
-  </si>
-  <si>
     <t>8-70</t>
   </si>
   <si>
@@ -616,9 +596,6 @@
     <t>H</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
     <t>HN</t>
   </si>
   <si>
@@ -628,9 +605,6 @@
     <t>I</t>
   </si>
   <si>
-    <t>Im</t>
-  </si>
-  <si>
     <t>J</t>
   </si>
   <si>
@@ -667,9 +641,6 @@
     <t>RA</t>
   </si>
   <si>
-    <t>RD</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
@@ -844,9 +815,6 @@
     <t>Kraken</t>
   </si>
   <si>
-    <t>Wriggle</t>
-  </si>
-  <si>
     <t>Hack Viking</t>
   </si>
   <si>
@@ -884,6 +852,18 @@
   </si>
   <si>
     <t>M</t>
+  </si>
+  <si>
+    <t>Bite Croc</t>
+  </si>
+  <si>
+    <t>Talon Ptera</t>
+  </si>
+  <si>
+    <t>Fort</t>
+  </si>
+  <si>
+    <t>Disk Ball</t>
   </si>
 </sst>
 </file>
@@ -919,9 +899,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1256,97 +1235,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -1356,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FD2484-138B-46C2-8DC8-D65120EDD404}">
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -1379,470 +1353,475 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G31" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -1852,82 +1831,87 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B0DAFC-13DE-46FF-A141-B64698BB60AB}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>261</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>270</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -1939,23 +1923,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A94B30-4A05-4913-869B-F7BDD7653D72}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1967,23 +1948,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894BAF9-FB4B-452B-BF9F-6F9CCE9B55C8}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1995,313 +1973,310 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408C55BD-65AC-48B0-AA3B-58B5A03C3D58}">
   <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2311,11 +2286,8 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F160EA4-7BEC-4BAF-AD34-499815061A5E}">
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2334,299 +2306,163 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63"/>
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2635,7 +2471,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -2643,10 +2479,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2654,7 +2490,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2662,7 +2498,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2670,7 +2506,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2678,111 +2514,111 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>271</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2790,71 +2626,71 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2862,7 +2698,7 @@
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2870,15 +2706,15 @@
         <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2886,7 +2722,7 @@
         <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2894,7 +2730,7 @@
         <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2902,7 +2738,7 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2910,31 +2746,31 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>264</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2942,90 +2778,71 @@
         <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>262</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>273</v>
-      </c>
-      <c r="B46" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>275</v>
-      </c>
-      <c r="B47" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>277</v>
-      </c>
-      <c r="B48" t="s">
-        <v>278</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B45" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B45">
+      <sortCondition ref="A1:A45"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\Backup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C359D0E2-88CC-4542-BBAC-8A734D98C16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D798F8-C456-4571-9557-8DCA4D33CCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="2" activeTab="7" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="273">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -864,6 +864,9 @@
   </si>
   <si>
     <t>Disk Ball</t>
+  </si>
+  <si>
+    <t>Hells</t>
   </si>
 </sst>
 </file>
@@ -1280,47 +1283,47 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D798F8-C456-4571-9557-8DCA4D33CCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{776933DB-A4BA-1743-8A8F-164777FEAC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" activeTab="1" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blades BX-UX'!$A$1:$A$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blades CX'!$A$1:$A$15</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="274">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -867,6 +867,9 @@
   </si>
   <si>
     <t>Hells</t>
+  </si>
+  <si>
+    <t>Mirage Clock</t>
   </si>
 </sst>
 </file>
@@ -922,7 +925,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1239,89 +1242,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>272</v>
       </c>
@@ -1333,163 +1336,163 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FD2484-138B-46C2-8DC8-D65120EDD404}">
-  <dimension ref="A1:G97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.80859375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -1497,334 +1500,339 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>253</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -1835,84 +1843,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B0DAFC-13DE-46FF-A141-B64698BB60AB}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>259</v>
       </c>
@@ -1925,19 +1933,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A94B30-4A05-4913-869B-F7BDD7653D72}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -1950,19 +1958,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894BAF9-FB4B-452B-BF9F-6F9CCE9B55C8}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1975,309 +1983,309 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408C55BD-65AC-48B0-AA3B-58B5A03C3D58}">
   <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>104</v>
       </c>
@@ -2290,179 +2298,179 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F160EA4-7BEC-4BAF-AD34-499815061A5E}">
   <dimension ref="A1:A35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -2475,12 +2483,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -2488,7 +2496,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2496,7 +2504,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2504,7 +2512,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -2512,7 +2520,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2520,7 +2528,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>271</v>
       </c>
@@ -2528,7 +2536,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2536,7 +2544,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2544,7 +2552,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2552,7 +2560,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -2560,7 +2568,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2568,7 +2576,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -2576,7 +2584,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -2584,7 +2592,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2592,7 +2600,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2600,7 +2608,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2608,7 +2616,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2616,7 +2624,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2624,7 +2632,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2632,7 +2640,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -2640,7 +2648,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2648,7 +2656,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -2656,7 +2664,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -2664,7 +2672,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -2672,7 +2680,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -2680,7 +2688,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -2688,7 +2696,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>266</v>
       </c>
@@ -2696,7 +2704,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -2704,7 +2712,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -2712,7 +2720,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -2720,7 +2728,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -2728,7 +2736,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -2736,7 +2744,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -2744,7 +2752,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -2752,7 +2760,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -2760,7 +2768,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -2768,7 +2776,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>264</v>
       </c>
@@ -2776,7 +2784,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -2784,7 +2792,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>262</v>
       </c>
@@ -2792,7 +2800,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>63</v>
       </c>
@@ -2800,7 +2808,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>65</v>
       </c>
@@ -2808,7 +2816,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -2816,7 +2824,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -2824,7 +2832,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>117</v>
       </c>
@@ -2832,7 +2840,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>70</v>
       </c>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{776933DB-A4BA-1743-8A8F-164777FEAC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" activeTab="1" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" activeTab="7" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="277">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -870,6 +870,12 @@
   </si>
   <si>
     <t>Mirage Clock</t>
+  </si>
+  <si>
+    <t>Wall Ball</t>
+  </si>
+  <si>
+    <t>WB</t>
   </si>
 </sst>
 </file>
@@ -2482,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.9140625" bestFit="1" customWidth="1"/>
@@ -2846,6 +2852,14 @@
       </c>
       <c r="B45" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>274</v>
+      </c>
+      <c r="B46" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{776933DB-A4BA-1743-8A8F-164777FEAC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" activeTab="7" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="278">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t>WB</t>
+  </si>
+  <si>
+    <t>Hornet</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -1333,6 +1336,11 @@
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="279">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -879,6 +879,9 @@
   </si>
   <si>
     <t>Hornet</t>
+  </si>
+  <si>
+    <t>Fox</t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -1341,6 +1344,11 @@
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{776933DB-A4BA-1743-8A8F-164777FEAC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64063A2F-5CC5-467A-8467-B96FAFE6768B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="25500" windowHeight="18375" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Bits!$A$1:$B$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blades BX-UX'!$A$1:$A$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blades BX-UX'!$A$1:$A$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blades CX'!$A$1:$A$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="276">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -296,9 +296,6 @@
     <t>Sphinx Cowl</t>
   </si>
   <si>
-    <t>Storm Pegasis</t>
-  </si>
-  <si>
     <t>Tricera Press</t>
   </si>
   <si>
@@ -362,9 +359,6 @@
     <t>Vertical</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Brave</t>
   </si>
   <si>
@@ -749,9 +743,6 @@
     <t>Optimus Prime</t>
   </si>
   <si>
-    <t>Perseus Dark</t>
-  </si>
-  <si>
     <t>Red Hulk</t>
   </si>
   <si>
@@ -882,6 +873,9 @@
   </si>
   <si>
     <t>Fox</t>
+  </si>
+  <si>
+    <t>Wriggle</t>
   </si>
 </sst>
 </file>
@@ -937,7 +931,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1254,101 +1248,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE9831B-6ED7-4E22-8757-F9C9A9FBD4DC}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -1358,503 +1352,493 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FD2484-138B-46C2-8DC8-D65120EDD404}">
-  <dimension ref="A1:G98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G96"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.80859375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="G31" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -1864,87 +1848,92 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B0DAFC-13DE-46FF-A141-B64698BB60AB}">
-  <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>259</v>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -1955,21 +1944,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A94B30-4A05-4913-869B-F7BDD7653D72}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1980,21 +1969,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894BAF9-FB4B-452B-BF9F-6F9CCE9B55C8}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2004,312 +1993,62 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408C55BD-65AC-48B0-AA3B-58B5A03C3D58}">
-  <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2320,179 +2059,179 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F160EA4-7BEC-4BAF-AD34-499815061A5E}">
   <dimension ref="A1:A35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -2505,377 +2244,377 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F6CE35-898A-4832-ADC2-08E81909FD24}">
   <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64063A2F-5CC5-467A-8467-B96FAFE6768B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09B4C1FF-4626-41CB-A85D-55DDEB59DF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="277">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t>Wriggle</t>
+  </si>
+  <si>
+    <t>Free</t>
   </si>
 </sst>
 </file>
@@ -1993,7 +1996,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408C55BD-65AC-48B0-AA3B-58B5A03C3D58}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2049,6 +2052,11 @@
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_BeybladeParts.xlsx
+++ b/Dataset_BeybladeParts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\challonge2csv-master\challonge2csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09B4C1FF-4626-41CB-A85D-55DDEB59DF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C394B02-3C83-4C65-AF1F-13B495EF2B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
+    <workbookView xWindow="5070" yWindow="3225" windowWidth="25500" windowHeight="18375" activeTab="5" xr2:uid="{C0602A2B-540B-4F49-BD8E-B6253569B973}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock Chips" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="278">
   <si>
     <t>Aero Pegasus</t>
   </si>
@@ -879,6 +879,9 @@
   </si>
   <si>
     <t>Free</t>
+  </si>
+  <si>
+    <t>Zillian</t>
   </si>
 </sst>
 </file>
@@ -1996,7 +1999,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408C55BD-65AC-48B0-AA3B-58B5A03C3D58}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2057,6 +2060,11 @@
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
